--- a/Golden_Dataset_Latest.xlsx
+++ b/Golden_Dataset_Latest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myrp-my.sharepoint.com/personal/23016385_myrp_edu_sg/Documents/Documents/1 FYP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="965" documentId="8_{DAA9AF50-9A98-447D-8C5C-C47E7DFE2939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{284553FA-6FEF-4375-9C59-D43AEA923C45}"/>
+  <xr:revisionPtr revIDLastSave="1008" documentId="8_{DAA9AF50-9A98-447D-8C5C-C47E7DFE2939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{082920D8-D14C-4A52-82BC-A44545A2DA35}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Golden_Dataset (2)" sheetId="7" state="hidden" r:id="rId1"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="455">
   <si>
     <t>Golden Dataset Instructions</t>
   </si>
@@ -276,9 +276,6 @@
   </si>
   <si>
     <t>Who are the Broad Members and describe their responsibilities?</t>
-  </si>
-  <si>
-    <t>changed the model to ibm/granite-4-h-small</t>
   </si>
   <si>
     <t>Agent</t>
@@ -911,13 +908,7 @@
     <t>total score</t>
   </si>
   <si>
-    <t>NOT SUPPORTED in my ENV</t>
-  </si>
-  <si>
     <t xml:space="preserve">  </t>
-  </si>
-  <si>
-    <t>using different template</t>
   </si>
   <si>
     <t>extra information are not accurate(Net cash from operating activities 22,809,489 not "Net cash generated from operating activities = $11,442,294"- hallucination</t>
@@ -1066,9 +1057,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Change Made</t>
-  </si>
-  <si>
     <t>The Company (Registration No. 201909251G) is incorporated in Singapore with its registered office and principal place of business at 6 Shenton Way, #17-10 OUE Downtown 2, Singapore 068809.</t>
   </si>
   <si>
@@ -1117,12 +1105,6 @@
     <t>correctly identified the Non-FI segment, conflated the total Group revenue</t>
   </si>
   <si>
-    <t>conclusion</t>
-  </si>
-  <si>
-    <t>Use restrictive Prompt template</t>
-  </si>
-  <si>
     <t>Mr Kevin Koo is the Executive Chairman and CEO of the Company. As stated in the context, as the CEO, Mr Kevin Koo is responsible for running the day-to-day business of the Group within the authorities delegated to him by the Board; ensuring implementation of policies and strategy across the Group as set by the Board; and leading the development of the Group's future strategy including identifying and assessing risks and opportunities for the growth of its business and reviewing the performance of its existing business.</t>
   </si>
   <si>
@@ -1349,9 +1331,6 @@
   </si>
   <si>
     <t>Llama3.1</t>
-  </si>
-  <si>
-    <t>llama3.1</t>
   </si>
   <si>
     <t xml:space="preserve">acknowledges that the chair message is present </t>
@@ -1463,9 +1442,6 @@
   </si>
   <si>
     <t>extra info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experiment 4 evaluated the impact of a highly restrictive prompt template on the performance of the llama 3.1. </t>
   </si>
   <si>
     <t>Exp #</t>
@@ -1577,6 +1553,12 @@
   </si>
   <si>
     <t>AI model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loose prompt </t>
+  </si>
+  <si>
+    <t>Restrictive prompt template</t>
   </si>
 </sst>
 </file>
@@ -2043,7 +2025,7 @@
         <v>14</v>
       </c>
       <c r="B1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1">
@@ -2071,7 +2053,7 @@
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G4" t="s">
         <v>62</v>
@@ -2088,13 +2070,13 @@
         <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="217.5">
@@ -2108,13 +2090,13 @@
         <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="87">
@@ -2128,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="188.5">
@@ -2148,13 +2130,13 @@
         <v>25</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="87">
@@ -2168,13 +2150,13 @@
         <v>26</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="29">
@@ -2188,13 +2170,13 @@
         <v>27</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="159.5">
@@ -2208,13 +2190,13 @@
         <v>28</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="391.5">
@@ -2228,13 +2210,13 @@
         <v>29</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="188.5">
@@ -2248,13 +2230,13 @@
         <v>30</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="174">
@@ -2268,13 +2250,13 @@
         <v>31</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="130.5">
@@ -2288,13 +2270,13 @@
         <v>33</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="101.5">
@@ -2308,13 +2290,13 @@
         <v>34</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="58">
@@ -2328,13 +2310,13 @@
         <v>35</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="43.5">
@@ -2348,13 +2330,13 @@
         <v>36</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="29">
@@ -2368,13 +2350,13 @@
         <v>37</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>173</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="116">
@@ -2388,16 +2370,16 @@
         <v>38</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="58">
@@ -2411,13 +2393,13 @@
         <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="261">
@@ -2431,13 +2413,13 @@
         <v>40</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="89.5" customHeight="1">
@@ -2451,13 +2433,13 @@
         <v>41</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="29">
@@ -2471,10 +2453,10 @@
         <v>42</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -2489,10 +2471,10 @@
         <v>44</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -2507,10 +2489,10 @@
         <v>45</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -2525,10 +2507,10 @@
         <v>46</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -2543,10 +2525,10 @@
         <v>47</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -2561,10 +2543,10 @@
         <v>48</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -2579,10 +2561,10 @@
         <v>50</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -2597,10 +2579,10 @@
         <v>51</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -2615,10 +2597,10 @@
         <v>52</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="F32" s="2"/>
     </row>
@@ -2633,10 +2615,10 @@
         <v>53</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -2651,10 +2633,10 @@
         <v>54</v>
       </c>
       <c r="D34" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -2671,13 +2653,13 @@
         <v>21</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D42" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="29">
@@ -2688,13 +2670,13 @@
         <v>32</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="43.5">
@@ -2705,13 +2687,13 @@
         <v>21</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="290">
@@ -2722,13 +2704,13 @@
         <v>49</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D45" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="58">
@@ -2739,13 +2721,13 @@
         <v>43</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D46" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -2759,7 +2741,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39FAB5A2-1336-4E06-BFF3-A6AF42029AC2}">
-  <dimension ref="A2:I34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="22.1796875" customWidth="1"/>
@@ -2771,17 +2753,25 @@
     <col min="7" max="9" width="41" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>56</v>
+      </c>
+    </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>452</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>253</v>
+        <v>450</v>
+      </c>
+      <c r="B3" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2810,7 +2800,7 @@
         <v>62</v>
       </c>
       <c r="I4" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="58">
@@ -2824,13 +2814,13 @@
         <v>22</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="G5">
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="I5">
         <f>SUM(G5:G34)</f>
@@ -2848,7 +2838,7 @@
         <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -2865,7 +2855,7 @@
         <v>24</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2882,7 +2872,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -2899,13 +2889,13 @@
         <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="72" customHeight="1">
@@ -2919,7 +2909,7 @@
         <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -2936,7 +2926,7 @@
         <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -2953,7 +2943,7 @@
         <v>29</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2967,10 +2957,10 @@
         <v>21</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -2987,7 +2977,7 @@
         <v>31</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3004,7 +2994,7 @@
         <v>33</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -3021,7 +3011,7 @@
         <v>34</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3038,13 +3028,13 @@
         <v>35</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="58">
@@ -3058,13 +3048,13 @@
         <v>36</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="43.5">
@@ -3078,7 +3068,7 @@
         <v>37</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3095,7 +3085,7 @@
         <v>38</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3112,7 +3102,7 @@
         <v>39</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -3129,13 +3119,13 @@
         <v>40</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="29">
@@ -3149,7 +3139,7 @@
         <v>41</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -3166,7 +3156,7 @@
         <v>42</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -3183,7 +3173,7 @@
         <v>44</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -3200,7 +3190,7 @@
         <v>45</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3217,13 +3207,13 @@
         <v>46</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="29">
@@ -3237,13 +3227,13 @@
         <v>47</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="29">
@@ -3257,7 +3247,7 @@
         <v>48</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3274,7 +3264,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -3291,7 +3281,7 @@
         <v>51</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -3308,7 +3298,7 @@
         <v>52</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -3325,7 +3315,7 @@
         <v>53</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -3342,7 +3332,7 @@
         <v>54</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -3445,7 +3435,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="D11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3475,19 +3465,19 @@
     </row>
     <row r="17" spans="1:13" ht="28">
       <c r="I17" s="12" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -3495,124 +3485,124 @@
         <v>13</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="L18" s="12">
         <v>30</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="28">
       <c r="I19" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="J19" s="13" t="s">
         <v>448</v>
       </c>
-      <c r="J19" s="13" t="s">
-        <v>456</v>
-      </c>
       <c r="K19" s="12" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="L19" s="12">
         <v>33</v>
       </c>
       <c r="M19" s="12" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="I20" s="12" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="L20" s="14">
         <v>33</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="28">
       <c r="A21" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="L21" s="12">
         <v>31</v>
       </c>
       <c r="M21" s="12" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="28">
       <c r="I22" s="12" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="L22" s="12">
         <v>32</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="28">
       <c r="I23" s="12" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="L23" s="12">
         <v>33</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="28">
       <c r="I24" s="12" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="L24" s="12">
         <v>29</v>
       </c>
       <c r="M24" s="12" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="14.5" customHeight="1">
@@ -3662,7 +3652,7 @@
         <v>14</v>
       </c>
       <c r="B1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1">
@@ -3704,10 +3694,10 @@
         <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="101.5">
@@ -3721,10 +3711,10 @@
         <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="29">
@@ -3738,10 +3728,10 @@
         <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="87">
@@ -3755,10 +3745,10 @@
         <v>25</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="101.5">
@@ -3772,10 +3762,10 @@
         <v>26</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -3789,10 +3779,10 @@
         <v>27</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="101.5">
@@ -3806,10 +3796,10 @@
         <v>28</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="116">
@@ -3823,10 +3813,10 @@
         <v>29</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="145">
@@ -3837,13 +3827,13 @@
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="58">
@@ -3857,10 +3847,10 @@
         <v>31</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="145">
@@ -3874,13 +3864,13 @@
         <v>33</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G15" s="2"/>
     </row>
@@ -3895,13 +3885,13 @@
         <v>34</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G16" s="2"/>
     </row>
@@ -3916,13 +3906,13 @@
         <v>35</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="G17" s="2"/>
     </row>
@@ -3937,13 +3927,13 @@
         <v>36</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="43.5">
@@ -3957,13 +3947,13 @@
         <v>37</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="130.5">
@@ -3977,10 +3967,10 @@
         <v>38</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F20" s="2"/>
     </row>
@@ -3995,10 +3985,10 @@
         <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="29">
@@ -4012,10 +4002,10 @@
         <v>40</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="89.5" customHeight="1">
@@ -4029,10 +4019,10 @@
         <v>41</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="58">
@@ -4046,10 +4036,10 @@
         <v>42</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="29">
@@ -4063,10 +4053,10 @@
         <v>44</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="29">
@@ -4080,13 +4070,13 @@
         <v>45</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="F26" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="43.5">
@@ -4100,13 +4090,13 @@
         <v>46</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F27" t="s">
         <v>202</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F27" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="58">
@@ -4120,10 +4110,10 @@
         <v>47</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="58">
@@ -4137,13 +4127,13 @@
         <v>48</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="F29" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="178.5" customHeight="1">
@@ -4157,10 +4147,10 @@
         <v>50</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="144.65" customHeight="1">
@@ -4174,10 +4164,10 @@
         <v>51</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="155.15" customHeight="1">
@@ -4191,10 +4181,10 @@
         <v>52</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="174">
@@ -4208,10 +4198,10 @@
         <v>53</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="58">
@@ -4225,10 +4215,10 @@
         <v>54</v>
       </c>
       <c r="D34" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="235" customHeight="1">
@@ -4293,7 +4283,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>55</v>
@@ -4309,7 +4299,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="B3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4338,7 +4328,7 @@
         <v>62</v>
       </c>
       <c r="I4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="29">
@@ -4352,7 +4342,7 @@
         <v>22</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -4373,13 +4363,13 @@
         <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="409.5">
@@ -4393,7 +4383,7 @@
         <v>24</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -4410,7 +4400,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -4427,7 +4417,7 @@
         <v>26</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -4444,13 +4434,13 @@
         <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="116">
@@ -4464,7 +4454,7 @@
         <v>28</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -4481,7 +4471,7 @@
         <v>29</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -4498,13 +4488,13 @@
         <v>30</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="29">
@@ -4518,7 +4508,7 @@
         <v>31</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -4535,13 +4525,13 @@
         <v>33</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="29">
@@ -4555,7 +4545,7 @@
         <v>34</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -4572,7 +4562,7 @@
         <v>35</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -4589,7 +4579,7 @@
         <v>36</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -4606,13 +4596,13 @@
         <v>37</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="87">
@@ -4626,7 +4616,7 @@
         <v>38</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -4643,7 +4633,7 @@
         <v>39</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -4660,7 +4650,7 @@
         <v>40</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -4677,7 +4667,7 @@
         <v>41</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -4694,13 +4684,13 @@
         <v>42</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="29">
@@ -4714,7 +4704,7 @@
         <v>44</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -4731,13 +4721,13 @@
         <v>45</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G26">
         <v>2</v>
       </c>
       <c r="H26" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="72.5">
@@ -4751,7 +4741,7 @@
         <v>46</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -4768,13 +4758,13 @@
         <v>47</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="304.5">
@@ -4788,13 +4778,13 @@
         <v>48</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="130.5">
@@ -4808,7 +4798,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -4825,13 +4815,13 @@
         <v>51</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G31">
         <v>2</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="116">
@@ -4845,7 +4835,7 @@
         <v>52</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -4862,7 +4852,7 @@
         <v>53</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -4879,7 +4869,7 @@
         <v>54</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -4888,7 +4878,7 @@
     <row r="35" spans="1:7">
       <c r="A35" s="2"/>
       <c r="B35" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C35" s="2"/>
       <c r="F35" s="1"/>
@@ -4997,10 +4987,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F3" s="3"/>
     </row>
@@ -5030,7 +5020,7 @@
         <v>62</v>
       </c>
       <c r="I4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -5044,7 +5034,7 @@
         <v>22</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -5065,13 +5055,13 @@
         <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="188.5">
@@ -5085,7 +5075,7 @@
         <v>24</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -5102,7 +5092,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -5119,13 +5109,13 @@
         <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="409.5">
@@ -5139,7 +5129,7 @@
         <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -5156,7 +5146,7 @@
         <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -5173,7 +5163,7 @@
         <v>29</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -5190,7 +5180,7 @@
         <v>30</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -5207,7 +5197,7 @@
         <v>31</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -5224,7 +5214,7 @@
         <v>33</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -5241,7 +5231,7 @@
         <v>34</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -5258,7 +5248,7 @@
         <v>35</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -5275,7 +5265,7 @@
         <v>36</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -5292,13 +5282,13 @@
         <v>37</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="87">
@@ -5312,13 +5302,13 @@
         <v>38</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="87.65" customHeight="1">
@@ -5332,7 +5322,7 @@
         <v>39</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -5350,13 +5340,13 @@
         <v>40</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -5370,7 +5360,7 @@
         <v>41</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -5388,13 +5378,13 @@
         <v>42</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="29">
@@ -5408,7 +5398,7 @@
         <v>44</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -5425,7 +5415,7 @@
         <v>45</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -5442,7 +5432,7 @@
         <v>46</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5459,16 +5449,16 @@
         <v>47</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I28" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="406">
@@ -5482,13 +5472,13 @@
         <v>48</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="130.5">
@@ -5502,13 +5492,13 @@
         <v>50</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="217.5">
@@ -5522,7 +5512,7 @@
         <v>51</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -5539,7 +5529,7 @@
         <v>52</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -5556,7 +5546,7 @@
         <v>53</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -5573,13 +5563,13 @@
         <v>54</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -5674,10 +5664,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="B3" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -5706,7 +5696,7 @@
         <v>62</v>
       </c>
       <c r="I4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="29">
@@ -5720,7 +5710,7 @@
         <v>22</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -5741,13 +5731,13 @@
         <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="116">
@@ -5761,7 +5751,7 @@
         <v>24</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -5778,7 +5768,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -5795,7 +5785,7 @@
         <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -5812,7 +5802,7 @@
         <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -5829,7 +5819,7 @@
         <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -5846,13 +5836,13 @@
         <v>29</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G12">
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="333.5">
@@ -5863,16 +5853,16 @@
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="43.5">
@@ -5886,7 +5876,7 @@
         <v>31</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -5903,7 +5893,7 @@
         <v>33</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -5920,7 +5910,7 @@
         <v>34</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -5937,13 +5927,13 @@
         <v>35</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="121" customHeight="1">
@@ -5957,13 +5947,13 @@
         <v>36</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="238" customHeight="1">
@@ -5977,13 +5967,13 @@
         <v>37</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G19">
         <v>2</v>
       </c>
       <c r="H19" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="211" customHeight="1">
@@ -5997,13 +5987,13 @@
         <v>38</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="43.5">
@@ -6017,7 +6007,7 @@
         <v>39</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -6034,7 +6024,7 @@
         <v>40</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -6051,7 +6041,7 @@
         <v>41</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -6085,13 +6075,13 @@
         <v>44</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="174">
@@ -6105,7 +6095,7 @@
         <v>45</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -6122,7 +6112,7 @@
         <v>46</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -6139,7 +6129,7 @@
         <v>47</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -6156,7 +6146,7 @@
         <v>48</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6173,7 +6163,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -6190,7 +6180,7 @@
         <v>51</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -6207,7 +6197,7 @@
         <v>52</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -6224,7 +6214,7 @@
         <v>53</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -6241,7 +6231,7 @@
         <v>54</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -6306,7 +6296,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -6335,7 +6325,7 @@
         <v>62</v>
       </c>
       <c r="I4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -6349,7 +6339,7 @@
         <v>22</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -6370,7 +6360,7 @@
         <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -6387,7 +6377,7 @@
         <v>24</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -6404,7 +6394,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -6421,7 +6411,7 @@
         <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -6438,7 +6428,7 @@
         <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -6455,7 +6445,7 @@
         <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -6472,7 +6462,7 @@
         <v>29</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -6486,16 +6476,16 @@
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -6509,7 +6499,7 @@
         <v>31</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -6526,7 +6516,7 @@
         <v>33</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -6543,7 +6533,7 @@
         <v>34</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -6560,7 +6550,7 @@
         <v>35</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -6577,13 +6567,13 @@
         <v>36</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
       <c r="H18" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="149.5" customHeight="1">
@@ -6597,7 +6587,7 @@
         <v>37</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -6614,7 +6604,7 @@
         <v>38</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -6631,7 +6621,7 @@
         <v>39</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -6648,7 +6638,7 @@
         <v>40</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -6665,7 +6655,7 @@
         <v>41</v>
       </c>
       <c r="F23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -6682,7 +6672,7 @@
         <v>42</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -6699,13 +6689,13 @@
         <v>44</v>
       </c>
       <c r="F25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="138" customHeight="1">
@@ -6719,7 +6709,7 @@
         <v>45</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -6737,7 +6727,7 @@
         <v>46</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -6755,7 +6745,7 @@
         <v>47</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -6772,7 +6762,7 @@
         <v>48</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6789,7 +6779,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -6806,7 +6796,7 @@
         <v>51</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -6823,13 +6813,13 @@
         <v>52</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="G32">
         <v>2</v>
       </c>
       <c r="H32" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="147.65" customHeight="1">
@@ -6843,7 +6833,7 @@
         <v>53</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -6860,7 +6850,7 @@
         <v>54</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -6905,7 +6895,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26057380-9B16-483D-B63A-C069861372E0}">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="22.1796875" customWidth="1"/>
@@ -6921,213 +6911,187 @@
       <c r="A1" t="s">
         <v>56</v>
       </c>
-      <c r="B1" t="s">
-        <v>399</v>
-      </c>
-      <c r="C1" t="s">
-        <v>321</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>304</v>
+        <v>452</v>
       </c>
       <c r="B2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C2" t="s">
-        <v>430</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>450</v>
       </c>
       <c r="B3" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>58</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E5" t="s">
         <v>59</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F5" t="s">
         <v>60</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G5" t="s">
         <v>61</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H5" t="s">
         <v>62</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <f>SUM(G6:G35)</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="72.5">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="43.5">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="29">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="43.5">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <f>SUM(G5:G34)</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="72.5">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="43.5">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="58">
+      <c r="A12">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="29">
-      <c r="A8">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="43.5">
-      <c r="A9">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="58">
-      <c r="A11">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -7135,16 +7099,16 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -7152,33 +7116,33 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -7186,16 +7150,16 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
         <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -7203,192 +7167,192 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19">
         <v>14</v>
       </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="62.15" customHeight="1">
-      <c r="A19">
+      <c r="F19" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="62.15" customHeight="1">
+      <c r="A20">
         <v>15</v>
       </c>
-      <c r="B19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
         <v>37</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20">
-        <v>16</v>
-      </c>
-      <c r="B20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" t="s">
-        <v>38</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
-      <c r="H20" t="s">
-        <v>359</v>
-      </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22">
         <v>17</v>
       </c>
-      <c r="B21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="29">
-      <c r="A22">
+      <c r="F22" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="29">
+      <c r="A23">
         <v>18</v>
       </c>
-      <c r="B22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G22">
+      <c r="F23" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="G23">
         <v>1</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23">
-        <v>19</v>
-      </c>
-      <c r="B23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
+      <c r="H23" s="2" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B24" t="s">
         <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
         <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
         <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B28" t="s">
         <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -7396,16 +7360,16 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B29" t="s">
         <v>43</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -7413,94 +7377,111 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="72.5">
+    <row r="31" spans="1:8">
       <c r="A31">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B31" t="s">
         <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="G31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="43.5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="72.5">
       <c r="A32">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
         <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="130.5">
+    <row r="33" spans="1:7" ht="43.5">
       <c r="A33">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B33" t="s">
         <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="G33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="130.5">
       <c r="A34">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34" t="s">
         <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>54</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>317</v>
+        <v>53</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>312</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
-      <c r="F35" s="2"/>
+    <row r="35" spans="1:7" ht="145">
+      <c r="A35">
+        <v>30</v>
+      </c>
+      <c r="B35" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" t="s">
+        <v>54</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="F36" s="2"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E5:E34">
+  <conditionalFormatting sqref="E6:E35">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -7512,7 +7493,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G34">
+  <conditionalFormatting sqref="G6:G35">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -7525,10 +7506,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E34 G5:G34" xr:uid="{16182D79-4A59-4DBD-B566-41B4A45DC4E4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:E35 G6:G35" xr:uid="{16182D79-4A59-4DBD-B566-41B4A45DC4E4}">
       <formula1>"0,1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D34" xr:uid="{74A94C9F-0BFC-479F-A0FA-5B6C0CEFE857}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D35" xr:uid="{74A94C9F-0BFC-479F-A0FA-5B6C0CEFE857}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7538,7 +7519,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFFD68B3-8045-4ADB-BB6D-513DEB2C3256}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="22.1796875" customWidth="1"/>
@@ -7559,383 +7540,366 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="B2" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="B3" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>58</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E5" t="s">
         <v>59</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F5" t="s">
         <v>60</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G5" t="s">
         <v>61</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H5" t="s">
         <v>62</v>
       </c>
-      <c r="I4" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="116">
-      <c r="A5">
+      <c r="I5" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="116">
+      <c r="A6">
         <v>1</v>
       </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5" t="s">
-        <v>429</v>
-      </c>
-      <c r="I5">
-        <f>SUM(G5:G34)</f>
+      <c r="F6" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6" t="s">
+        <v>422</v>
+      </c>
+      <c r="I6">
+        <f>SUM(G6:G35)</f>
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="159.5">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
+    <row r="7" spans="1:9" ht="159.5">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="377">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="G7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="87">
+    <row r="8" spans="1:9" ht="377">
       <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="87">
+      <c r="A9">
         <v>4</v>
       </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F9" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="43.5">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="87">
+      <c r="A12">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="409.5" customHeight="1">
+      <c r="A14">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>296</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="43.5">
-      <c r="A9">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="29">
+      <c r="A15">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="43.5">
+      <c r="A16">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="323.14999999999998" customHeight="1">
+      <c r="A17">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="174">
+      <c r="A18">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>329</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="87">
-      <c r="A11">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="409.5" customHeight="1">
-      <c r="A13">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" t="s">
-        <v>299</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="29">
-      <c r="A14">
-        <v>10</v>
-      </c>
-      <c r="B14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="43.5">
-      <c r="A15">
-        <v>11</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="323.14999999999998" customHeight="1">
-      <c r="A16">
-        <v>12</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="174">
-      <c r="A17">
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="72.5">
-      <c r="A18">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>284</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="203">
+      <c r="H18" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="72.5">
       <c r="A19">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="203">
+      <c r="A20">
         <v>15</v>
       </c>
-      <c r="B19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
         <v>37</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="159.5">
-      <c r="A20">
+      <c r="F20" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="159.5">
+      <c r="A21">
         <v>16</v>
       </c>
-      <c r="B20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="G20">
+      <c r="F21" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G21">
         <v>1</v>
       </c>
-      <c r="H20" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="58">
-      <c r="A21">
+      <c r="H21" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="58">
+      <c r="A22">
         <v>17</v>
       </c>
-      <c r="B21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="72.5">
-      <c r="A22">
+      <c r="F22" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="72.5">
+      <c r="A23">
         <v>18</v>
       </c>
-      <c r="B22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23">
-        <v>19</v>
-      </c>
-      <c r="B23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" t="s">
-        <v>41</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>74</v>
+        <v>284</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -7943,196 +7907,213 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
+        <v>19</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25">
         <v>20</v>
       </c>
-      <c r="B24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
         <v>42</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F25" s="10">
         <v>3916630</v>
       </c>
-      <c r="G24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="101.5">
-      <c r="A25">
-        <v>21</v>
-      </c>
-      <c r="B25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" t="s">
-        <v>44</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="101.5">
       <c r="A26">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
         <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>339</v>
+        <v>285</v>
       </c>
       <c r="G26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="159.5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="145">
       <c r="A27">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
         <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="72.5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="159.5">
       <c r="A28">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B28" t="s">
         <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>291</v>
+        <v>334</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" ht="116">
+      <c r="H28" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="72.5">
       <c r="A29">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B29" t="s">
         <v>43</v>
       </c>
       <c r="C29" t="s">
+        <v>47</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="116">
+      <c r="A30">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" t="s">
         <v>48</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="G29">
+      <c r="F30" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="G30">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="101.5">
-      <c r="A30">
+    <row r="31" spans="1:8" ht="101.5">
+      <c r="A31">
         <v>26</v>
-      </c>
-      <c r="B30" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" t="s">
-        <v>50</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="203">
-      <c r="A31">
-        <v>27</v>
       </c>
       <c r="B31" t="s">
         <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>342</v>
+        <v>290</v>
       </c>
       <c r="G31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="72.5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="203">
       <c r="A32">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
         <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="G32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="188.5">
+    <row r="33" spans="1:7" ht="72.5">
       <c r="A33">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B33" t="s">
         <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="G33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="217.5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="188.5">
       <c r="A34">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34" t="s">
         <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
     </row>
+    <row r="35" spans="1:7" ht="217.5">
+      <c r="A35">
+        <v>30</v>
+      </c>
+      <c r="B35" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" t="s">
+        <v>54</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E5:E34">
+  <conditionalFormatting sqref="E6:E35">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -8144,7 +8125,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G34">
+  <conditionalFormatting sqref="G6:G35">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -8157,10 +8138,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D34" xr:uid="{3E01F5C4-D546-45B6-952D-D233FEAA011C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D35" xr:uid="{3E01F5C4-D546-45B6-952D-D233FEAA011C}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E34 G5:G34" xr:uid="{DA1DBE40-3562-4C2D-97EF-4CA375619A8D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:E35 G6:G35" xr:uid="{DA1DBE40-3562-4C2D-97EF-4CA375619A8D}">
       <formula1>"0,1,2"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8169,16 +8150,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9fd2e45c-4d37-4fa6-a2bd-508f3d0c042d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100677A0709C7E4034F9730662C83955827" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2a340845f4dfacc905c547fa3ef7bf25">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9fd2e45c-4d37-4fa6-a2bd-508f3d0c042d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bdfe8d45d66d69620af7b1c877e3cb1c" ns2:_="">
     <xsd:import namespace="9fd2e45c-4d37-4fa6-a2bd-508f3d0c042d"/>
@@ -8350,7 +8321,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -8359,18 +8330,17 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68588167-E3A9-4BD3-8EB6-FC300989CC62}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="9fd2e45c-4d37-4fa6-a2bd-508f3d0c042d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9fd2e45c-4d37-4fa6-a2bd-508f3d0c042d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF14994-A7FA-42C9-B680-A8CE021FA97D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8389,10 +8359,21 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4AC7440-88AB-454F-8F4C-108DE229EA70}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68588167-E3A9-4BD3-8EB6-FC300989CC62}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="9fd2e45c-4d37-4fa6-a2bd-508f3d0c042d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
